--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>LARRACILLA</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
@@ -100,6 +103,21 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TELE</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>GERARDO</t>
   </si>
   <si>
@@ -121,6 +139,21 @@
     <t>TEZOCO</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>MONSERRAT</t>
+  </si>
+  <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
@@ -140,6 +173,21 @@
   </si>
   <si>
     <t>MARISOL</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>BETSABETH</t>
   </si>
 </sst>
 </file>
@@ -914,7 +962,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -946,22 +994,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920262</v>
+        <v>22330051920340</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -969,16 +1017,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920264</v>
+        <v>22330051920262</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -992,16 +1040,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920265</v>
+        <v>22330051920264</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1015,16 +1063,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920270</v>
+        <v>22330051920265</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1038,16 +1086,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920273</v>
+        <v>22330051920270</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1061,16 +1109,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920286</v>
+        <v>22330051920273</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1084,16 +1132,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920288</v>
+        <v>22330051920286</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1103,6 +1151,144 @@
       </c>
       <c r="G8">
         <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920288</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" t="s">
+        <v>51</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920031</v>
+      </c>
+      <c r="B10" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" t="s">
+        <v>52</v>
+      </c>
+      <c r="E10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" t="s">
+        <v>11</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920034</v>
+      </c>
+      <c r="B11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" t="s">
+        <v>11</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920043</v>
+      </c>
+      <c r="B12" t="s">
+        <v>29</v>
+      </c>
+      <c r="C12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D12" t="s">
+        <v>54</v>
+      </c>
+      <c r="E12" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920049</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="s">
+        <v>42</v>
+      </c>
+      <c r="D13" t="s">
+        <v>55</v>
+      </c>
+      <c r="E13" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" t="s">
+        <v>11</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920121</v>
+      </c>
+      <c r="B14" t="s">
+        <v>31</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G14">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -97,6 +97,15 @@
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -133,6 +142,12 @@
     <t>CONTRERAS</t>
   </si>
   <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
@@ -167,6 +182,15 @@
   </si>
   <si>
     <t>JOSE</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
   </si>
   <si>
     <t>ABRAHAM</t>
@@ -962,7 +986,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1000,10 +1024,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1023,10 +1047,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1046,10 +1070,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1069,10 +1093,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1092,10 +1116,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1115,10 +1139,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1132,16 +1156,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920286</v>
+        <v>22330051920276</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1155,16 +1179,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920288</v>
+        <v>22330051920407</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1178,22 +1202,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920031</v>
+        <v>22330051920282</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1201,22 +1225,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920034</v>
+        <v>22330051920286</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1224,22 +1248,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920043</v>
+        <v>22330051920288</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1247,16 +1271,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920049</v>
+        <v>22330051920031</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>23</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1270,24 +1294,93 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
+        <v>22330051920034</v>
+      </c>
+      <c r="B14" t="s">
+        <v>22</v>
+      </c>
+      <c r="C14" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" t="s">
+        <v>61</v>
+      </c>
+      <c r="E14" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" t="s">
+        <v>11</v>
+      </c>
+      <c r="G14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920043</v>
+      </c>
+      <c r="B15" t="s">
+        <v>32</v>
+      </c>
+      <c r="C15" t="s">
+        <v>46</v>
+      </c>
+      <c r="D15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" t="s">
+        <v>11</v>
+      </c>
+      <c r="G15">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920049</v>
+      </c>
+      <c r="B16" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" t="s">
+        <v>63</v>
+      </c>
+      <c r="E16" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" t="s">
+        <v>11</v>
+      </c>
+      <c r="G16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17">
         <v>22330051920121</v>
       </c>
-      <c r="B14" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" t="s">
-        <v>56</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
+      <c r="B17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" t="s">
         <v>10</v>
       </c>
-      <c r="G14">
+      <c r="G17">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="68">
   <si>
     <t>Mat</t>
   </si>
@@ -85,133 +85,142 @@
     <t>BACILIO</t>
   </si>
   <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
+    <t>PALOMINO</t>
+  </si>
+  <si>
+    <t>VENTURA</t>
+  </si>
+  <si>
+    <t>TELE</t>
   </si>
   <si>
     <t>OFICIAL</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>TELE</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
     <t>GERARDO</t>
   </si>
   <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>EVANGELISTA</t>
+  </si>
+  <si>
+    <t>REYES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>SALOMON</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>CONTRERAS</t>
   </si>
   <si>
     <t>TELLEZ</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
     <t>VELAZQUEZ</t>
   </si>
   <si>
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
     <t>MONSERRAT</t>
   </si>
   <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>MARIA DE LOS ANGELES</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>OSCAR</t>
+  </si>
+  <si>
+    <t>SAUL KOURCHENKOV</t>
+  </si>
+  <si>
+    <t>RICARDO</t>
+  </si>
+  <si>
+    <t>CARLOS YAEL</t>
+  </si>
+  <si>
+    <t>AARON MIGUEL</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>BETSABETH</t>
+  </si>
+  <si>
     <t>ANA KAREN</t>
   </si>
   <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>MARIA DE LOS ANGELES</t>
-  </si>
-  <si>
     <t>JOSE</t>
   </si>
   <si>
-    <t>ERIK</t>
-  </si>
-  <si>
     <t>OZIEL</t>
   </si>
   <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
     <t>ABRAHAM</t>
   </si>
   <si>
     <t>MARISOL</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>BETSABETH</t>
   </si>
 </sst>
 </file>
@@ -986,7 +995,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1024,10 +1033,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1047,10 +1056,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1064,16 +1073,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920264</v>
+        <v>22330051920265</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1087,16 +1096,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920270</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1110,16 +1119,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920270</v>
+        <v>22330051920276</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1133,7 +1142,7 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920273</v>
+        <v>22330051920277</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1142,7 +1151,7 @@
         <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1156,16 +1165,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920276</v>
+        <v>22330051920282</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1179,22 +1188,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920407</v>
+        <v>22330051920031</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>22</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1202,7 +1211,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920282</v>
+        <v>22330051920034</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
@@ -1211,13 +1220,13 @@
         <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1225,7 +1234,7 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920286</v>
+        <v>22330051920043</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
@@ -1234,13 +1243,13 @@
         <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1248,7 +1257,7 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920288</v>
+        <v>22330051920049</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
@@ -1257,13 +1266,13 @@
         <v>44</v>
       </c>
       <c r="D12" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1271,116 +1280,139 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920031</v>
+        <v>22330051920121</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="D13" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G13">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920034</v>
+        <v>22330051920264</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920043</v>
+        <v>22330051920273</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920049</v>
+        <v>22330051920407</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920121</v>
+        <v>22330051920286</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18">
+        <v>22330051920288</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>12</v>
+      </c>
+      <c r="G18">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="80">
   <si>
     <t>Mat</t>
   </si>
@@ -49,10 +49,10 @@
     <t>TEMAS DE FILOSOFÍA</t>
   </si>
   <si>
-    <t>2ALCM</t>
-  </si>
-  <si>
-    <t>2BEM</t>
+    <t>2AEM</t>
+  </si>
+  <si>
+    <t>2BLCM</t>
   </si>
   <si>
     <t>2APV</t>
@@ -79,7 +79,7 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>LARRACILLA</t>
+    <t>CARRERA</t>
   </si>
   <si>
     <t>BACILIO</t>
@@ -100,19 +100,34 @@
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>CASTILLO</t>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>PALOMINO</t>
-  </si>
-  <si>
-    <t>VENTURA</t>
-  </si>
-  <si>
-    <t>TELE</t>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
   </si>
   <si>
     <t>OFICIAL</t>
@@ -127,7 +142,10 @@
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>GOMEZ</t>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
   </si>
   <si>
     <t>GERARDO</t>
@@ -136,28 +154,34 @@
     <t>CASASOLA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
     <t>EVANGELISTA</t>
   </si>
   <si>
-    <t>REYES</t>
+    <t>BAEZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>SALOMON</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
   </si>
   <si>
     <t>CONTRERAS</t>
@@ -172,7 +196,7 @@
     <t>TEZOCO</t>
   </si>
   <si>
-    <t>MONSERRAT</t>
+    <t>ANA KAREN</t>
   </si>
   <si>
     <t>LUIS JAVIER</t>
@@ -193,22 +217,31 @@
     <t>SAUL KOURCHENKOV</t>
   </si>
   <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
-    <t>CARLOS YAEL</t>
-  </si>
-  <si>
-    <t>AARON MIGUEL</t>
+    <t>ESTEFANY CELESTE</t>
+  </si>
+  <si>
+    <t>XIMENA</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
+    <t>MELISA VIANNEY</t>
   </si>
   <si>
     <t>DANIEL</t>
   </si>
   <si>
-    <t>BETSABETH</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>ANGELO</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>JOSE FRANCISCO</t>
   </si>
   <si>
     <t>JOSE</t>
@@ -221,6 +254,9 @@
   </si>
   <si>
     <t>MARISOL</t>
+  </si>
+  <si>
+    <t>DARA NAOMI</t>
   </si>
 </sst>
 </file>
@@ -618,22 +654,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>88.37</v>
+        <v>73.53</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -644,22 +680,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>83.78</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -761,13 +797,13 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="E2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -784,13 +820,13 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -892,22 +928,22 @@
         <v>10</v>
       </c>
       <c r="C2">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>88.37</v>
+        <v>73.53</v>
       </c>
       <c r="H2">
-        <v>8.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -918,22 +954,22 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F3">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>83.78</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -995,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G18"/>
+  <dimension ref="A1:G24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1027,16 +1063,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920340</v>
+        <v>22330051920007</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1056,10 +1092,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1079,10 +1115,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1102,10 +1138,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1125,10 +1161,10 @@
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1148,10 +1184,10 @@
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1171,10 +1207,10 @@
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1188,16 +1224,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920031</v>
+        <v>22330051920126</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1211,16 +1247,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920034</v>
+        <v>22330051920132</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1234,16 +1270,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920043</v>
+        <v>22330051920354</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1257,16 +1293,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920049</v>
+        <v>22330051920145</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1280,16 +1316,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920121</v>
+        <v>22330051920003</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1303,22 +1339,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920264</v>
+        <v>22330051920006</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14">
         <v>1</v>
@@ -1326,22 +1362,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920273</v>
+        <v>22330051920011</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G15">
         <v>1</v>
@@ -1349,22 +1385,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920407</v>
+        <v>22330051920017</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1372,22 +1408,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920286</v>
+        <v>22330051920018</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1395,24 +1431,162 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
+        <v>22330051920021</v>
+      </c>
+      <c r="B18" t="s">
+        <v>36</v>
+      </c>
+      <c r="C18" t="s">
+        <v>33</v>
+      </c>
+      <c r="D18" t="s">
+        <v>74</v>
+      </c>
+      <c r="E18" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" t="s">
+        <v>10</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7">
+      <c r="A19">
+        <v>22330051920264</v>
+      </c>
+      <c r="B19" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>12</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>22330051920273</v>
+      </c>
+      <c r="B20" t="s">
+        <v>37</v>
+      </c>
+      <c r="C20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>12</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>22330051920407</v>
+      </c>
+      <c r="B21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" t="s">
+        <v>56</v>
+      </c>
+      <c r="D21" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>12</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
+        <v>22330051920286</v>
+      </c>
+      <c r="B22" t="s">
+        <v>39</v>
+      </c>
+      <c r="C22" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>12</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
         <v>22330051920288</v>
       </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
+      <c r="B23" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D23" t="s">
+        <v>78</v>
+      </c>
+      <c r="E23" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" t="s">
         <v>12</v>
       </c>
-      <c r="G18">
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
+        <v>22330051920344</v>
+      </c>
+      <c r="B24" t="s">
+        <v>41</v>
+      </c>
+      <c r="C24" t="s">
+        <v>42</v>
+      </c>
+      <c r="D24" t="s">
+        <v>79</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -680,7 +680,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -689,10 +689,10 @@
         <v>14</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>65.84999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -820,13 +820,13 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -954,7 +954,7 @@
         <v>11</v>
       </c>
       <c r="C3">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -963,10 +963,10 @@
         <v>14</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>65.84999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="H3">
         <v>6.6</v>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
   <si>
     <t>Mat</t>
   </si>
@@ -79,16 +79,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
     <t>BACILIO</t>
   </si>
   <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
+    <t>OLMEDO</t>
   </si>
   <si>
     <t>RAMIREZ</t>
@@ -97,52 +103,46 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>GARCIA</t>
@@ -157,55 +157,55 @@
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>EVANGELISTA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>TELLEZ</t>
+  </si>
+  <si>
+    <t>VELAZQUEZ</t>
+  </si>
+  <si>
+    <t>TEZOCO</t>
   </si>
   <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
+    <t>ANGELO</t>
   </si>
   <si>
     <t>ANA KAREN</t>
   </si>
   <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
-    <t>MARIA DE LOS ANGELES</t>
+    <t>SERGIO FARITH</t>
   </si>
   <si>
     <t>ERIK</t>
@@ -214,34 +214,25 @@
     <t>OSCAR</t>
   </si>
   <si>
-    <t>SAUL KOURCHENKOV</t>
-  </si>
-  <si>
-    <t>ESTEFANY CELESTE</t>
-  </si>
-  <si>
     <t>XIMENA</t>
   </si>
   <si>
+    <t>AZUL ARIADNA</t>
+  </si>
+  <si>
+    <t>MELISA VIANNEY</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
     <t>KEVIN</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>EDER</t>
-  </si>
-  <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>JOSE FRANCISCO</t>
   </si>
   <si>
     <t>JOSE</t>
@@ -1031,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G24"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,16 +1054,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920007</v>
+        <v>22330051920011</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1086,22 +1077,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920262</v>
+        <v>22330051920007</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1109,22 +1100,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920265</v>
+        <v>22330051920021</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="D4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1132,16 +1123,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920270</v>
+        <v>22330051920262</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1155,16 +1146,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920276</v>
+        <v>22330051920265</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1178,16 +1169,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920277</v>
+        <v>22330051920367</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1201,16 +1192,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920282</v>
+        <v>22330051920276</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1224,22 +1215,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920126</v>
+        <v>22330051920277</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1253,10 +1244,10 @@
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="D10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1270,16 +1261,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920354</v>
+        <v>22330051920353</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1299,10 +1290,10 @@
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1322,10 +1313,10 @@
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="D13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1345,10 +1336,10 @@
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="D14" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1362,16 +1353,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>22330051920011</v>
+        <v>22330051920017</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1385,16 +1376,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>22330051920017</v>
+        <v>22330051920018</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D16" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1408,22 +1399,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>22330051920018</v>
+        <v>22330051920264</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="C17" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1431,22 +1422,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>22330051920021</v>
+        <v>22330051920273</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1454,16 +1445,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>22330051920264</v>
+        <v>22330051920407</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="D19" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1477,16 +1468,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>22330051920273</v>
+        <v>22330051920286</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="D20" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1500,16 +1491,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>22330051920407</v>
+        <v>22330051920288</v>
       </c>
       <c r="B21" t="s">
         <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1523,22 +1514,22 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>22330051920286</v>
+        <v>22330051920344</v>
       </c>
       <c r="B22" t="s">
         <v>39</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
       </c>
       <c r="F22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -1546,47 +1537,24 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>22330051920288</v>
+        <v>22330051920354</v>
       </c>
       <c r="B23" t="s">
         <v>40</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D23" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="E23" t="s">
         <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920344</v>
-      </c>
-      <c r="B24" t="s">
-        <v>41</v>
-      </c>
-      <c r="C24" t="s">
-        <v>42</v>
-      </c>
-      <c r="D24" t="s">
-        <v>79</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>11</v>
-      </c>
-      <c r="G24">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
   <si>
     <t>Mat</t>
   </si>
@@ -79,121 +79,79 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>BACILIO</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>OLMEDO</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
+    <t>GERARDO</t>
+  </si>
+  <si>
+    <t>------</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>SALAS</t>
-  </si>
-  <si>
     <t>TEXOCO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>JERONIMO</t>
   </si>
   <si>
     <t>AVELINO</t>
   </si>
   <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>TELLEZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>TEZOCO</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>ANGELO</t>
-  </si>
-  <si>
-    <t>ANA KAREN</t>
+    <t>EDER</t>
+  </si>
+  <si>
+    <t>DIEGO JESUS</t>
   </si>
   <si>
     <t>JOSE FRANCISCO</t>
@@ -202,49 +160,25 @@
     <t>LUIS JAVIER</t>
   </si>
   <si>
+    <t>CARLOS DAVID</t>
+  </si>
+  <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
-    <t>SERGIO FARITH</t>
+    <t>KATIA PAOLA</t>
   </si>
   <si>
     <t>ERIK</t>
   </si>
   <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>XIMENA</t>
-  </si>
-  <si>
-    <t>AZUL ARIADNA</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
     <t>DANIEL</t>
   </si>
   <si>
-    <t>EDER</t>
-  </si>
-  <si>
     <t>LUIS</t>
   </si>
   <si>
     <t>KEVIN</t>
-  </si>
-  <si>
-    <t>JOSE</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>ABRAHAM</t>
-  </si>
-  <si>
-    <t>MARISOL</t>
   </si>
   <si>
     <t>DARA NAOMI</t>
@@ -791,16 +725,19 @@
         <v>34</v>
       </c>
       <c r="D2">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>73.53</v>
+      </c>
+      <c r="H2">
+        <v>6.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -814,16 +751,19 @@
         <v>42</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>69.05</v>
+      </c>
+      <c r="H3">
+        <v>6.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -837,16 +777,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>50</v>
+      </c>
+      <c r="H4">
+        <v>5.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -860,16 +803,19 @@
         <v>19</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H5">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -951,16 +897,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>66.67</v>
+        <v>69.05</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -977,16 +923,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F4">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>26.67</v>
+        <v>50</v>
       </c>
       <c r="H4">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1003,16 +949,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G5">
-        <v>100</v>
+        <v>89.47</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -1022,7 +968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1054,16 +1000,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920011</v>
+        <v>22330051920006</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1077,16 +1023,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920007</v>
+        <v>22330051920015</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1106,10 +1052,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1129,10 +1075,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1146,16 +1092,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920265</v>
+        <v>22330051920409</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1169,16 +1115,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920367</v>
+        <v>22330051920265</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1192,16 +1138,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920276</v>
+        <v>22330051920411</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
         <v>37</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1215,16 +1161,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920277</v>
+        <v>22330051920276</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1238,91 +1184,91 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920132</v>
+        <v>22330051920003</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920353</v>
+        <v>22330051920017</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="D11" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G11">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920145</v>
+        <v>22330051920018</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920003</v>
+        <v>22330051920344</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>21</v>
       </c>
       <c r="D13" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G13">
         <v>1</v>
@@ -1330,231 +1276,24 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>22330051920006</v>
+        <v>22330051920354</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="D14" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920017</v>
-      </c>
-      <c r="B15" t="s">
-        <v>33</v>
-      </c>
-      <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>70</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>10</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920018</v>
-      </c>
-      <c r="B16" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" t="s">
-        <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>71</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920264</v>
-      </c>
-      <c r="B17" t="s">
-        <v>20</v>
-      </c>
-      <c r="C17" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" t="s">
-        <v>58</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>12</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920273</v>
-      </c>
-      <c r="B18" t="s">
-        <v>35</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="D18" t="s">
-        <v>72</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>12</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920407</v>
-      </c>
-      <c r="B19" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" t="s">
-        <v>53</v>
-      </c>
-      <c r="D19" t="s">
-        <v>73</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>12</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920286</v>
-      </c>
-      <c r="B20" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" t="s">
-        <v>74</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>12</v>
-      </c>
-      <c r="G20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920288</v>
-      </c>
-      <c r="B21" t="s">
-        <v>38</v>
-      </c>
-      <c r="C21" t="s">
-        <v>55</v>
-      </c>
-      <c r="D21" t="s">
-        <v>75</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>12</v>
-      </c>
-      <c r="G21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920344</v>
-      </c>
-      <c r="B22" t="s">
-        <v>39</v>
-      </c>
-      <c r="C22" t="s">
-        <v>42</v>
-      </c>
-      <c r="D22" t="s">
-        <v>76</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>11</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920354</v>
-      </c>
-      <c r="B23" t="s">
-        <v>40</v>
-      </c>
-      <c r="C23" t="s">
-        <v>56</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>11</v>
-      </c>
-      <c r="G23">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
   <si>
     <t>Mat</t>
   </si>
@@ -79,9 +79,6 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
     <t>GARCIA</t>
   </si>
   <si>
@@ -112,9 +109,6 @@
     <t>SOLANO</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
     <t>QUERO</t>
   </si>
   <si>
@@ -124,33 +118,30 @@
     <t>GERARDO</t>
   </si>
   <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>TEXOCO</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
+  </si>
+  <si>
     <t>------</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>EDER</t>
-  </si>
-  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
@@ -160,25 +151,25 @@
     <t>LUIS JAVIER</t>
   </si>
   <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>KATIA PAOLA</t>
+  </si>
+  <si>
+    <t>ERIK</t>
+  </si>
+  <si>
+    <t>DANIEL</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
     <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
   </si>
   <si>
     <t>DARA NAOMI</t>
@@ -968,7 +959,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1000,16 +991,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920006</v>
+        <v>22330051920015</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1023,16 +1014,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920015</v>
+        <v>22330051920021</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1046,22 +1037,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920021</v>
+        <v>22330051920262</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1069,16 +1060,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920262</v>
+        <v>22330051920265</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1092,16 +1083,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920409</v>
+        <v>22330051920411</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1115,16 +1106,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920265</v>
+        <v>22330051920276</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D7" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1138,62 +1129,62 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920411</v>
+        <v>22330051920003</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920276</v>
+        <v>22330051920017</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D9" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G9">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920003</v>
+        <v>22330051920018</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D10" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1207,22 +1198,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920017</v>
+        <v>22330051920409</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>1</v>
@@ -1230,22 +1221,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920018</v>
+        <v>22330051920344</v>
       </c>
       <c r="B12" t="s">
         <v>28</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
+        <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>1</v>
@@ -1253,16 +1244,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920344</v>
+        <v>22330051920354</v>
       </c>
       <c r="B13" t="s">
         <v>29</v>
       </c>
       <c r="C13" t="s">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D13" t="s">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1271,29 +1262,6 @@
         <v>11</v>
       </c>
       <c r="G13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920354</v>
-      </c>
-      <c r="B14" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" t="s">
-        <v>42</v>
-      </c>
-      <c r="D14" t="s">
-        <v>53</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
   <si>
     <t>Mat</t>
   </si>
@@ -82,9 +82,6 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>MEJIA</t>
-  </si>
-  <si>
     <t>BACILIO</t>
   </si>
   <si>
@@ -94,6 +91,9 @@
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>SOLANO</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -106,15 +106,9 @@
     <t>CABRERA</t>
   </si>
   <si>
-    <t>SOLANO</t>
-  </si>
-  <si>
     <t>QUERO</t>
   </si>
   <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
     <t>GERARDO</t>
   </si>
   <si>
@@ -127,6 +121,9 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
     <t>TEXOCO</t>
   </si>
   <si>
@@ -139,15 +136,9 @@
     <t>------</t>
   </si>
   <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
-    <t>JOSE FRANCISCO</t>
-  </si>
-  <si>
     <t>LUIS JAVIER</t>
   </si>
   <si>
@@ -160,13 +151,13 @@
     <t>ERIK</t>
   </si>
   <si>
+    <t>KEVIN</t>
+  </si>
+  <si>
     <t>DANIEL</t>
   </si>
   <si>
     <t>LUIS</t>
-  </si>
-  <si>
-    <t>KEVIN</t>
   </si>
   <si>
     <t>CARLOS DAVID</t>
@@ -959,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -997,10 +988,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1014,22 +1005,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920021</v>
+        <v>22330051920262</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1037,16 +1028,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920262</v>
+        <v>22330051920265</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1060,16 +1051,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920265</v>
+        <v>22330051920411</v>
       </c>
       <c r="B5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1083,16 +1074,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920411</v>
+        <v>22330051920276</v>
       </c>
       <c r="B6" t="s">
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1106,22 +1097,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920276</v>
+        <v>22330051920354</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1135,10 +1126,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1158,10 +1149,10 @@
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1181,10 +1172,10 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1204,10 +1195,10 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1230,7 +1221,7 @@
         <v>20</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1239,29 +1230,6 @@
         <v>11</v>
       </c>
       <c r="G12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920354</v>
-      </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>40</v>
-      </c>
-      <c r="D13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>11</v>
-      </c>
-      <c r="G13">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -82,88 +82,55 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>BACILIO</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>SOLANO</t>
   </si>
   <si>
+    <t>TORRES</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
     <t>GUERRA</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
     <t>QUERO</t>
   </si>
   <si>
-    <t>GERARDO</t>
-  </si>
-  <si>
     <t>CASASOLA</t>
   </si>
   <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>TEXOCO</t>
+    <t>SALAS</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
   </si>
   <si>
     <t>JERONIMO</t>
   </si>
   <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>------</t>
-  </si>
-  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
-    <t>LUIS JAVIER</t>
-  </si>
-  <si>
     <t>SERGIO IVAN</t>
   </si>
   <si>
-    <t>KATIA PAOLA</t>
-  </si>
-  <si>
-    <t>ERIK</t>
-  </si>
-  <si>
     <t>KEVIN</t>
   </si>
   <si>
-    <t>DANIEL</t>
+    <t>MELISA VIANNEY</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
   </si>
   <si>
     <t>LUIS</t>
-  </si>
-  <si>
-    <t>CARLOS DAVID</t>
-  </si>
-  <si>
-    <t>DARA NAOMI</t>
   </si>
 </sst>
 </file>
@@ -853,16 +820,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>73.53</v>
+        <v>85.29000000000001</v>
       </c>
       <c r="H2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -879,16 +846,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F3">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>69.05</v>
+        <v>76.19</v>
       </c>
       <c r="H3">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -905,16 +872,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>50</v>
+        <v>73.33</v>
       </c>
       <c r="H4">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -931,16 +898,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G5">
-        <v>89.47</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H5">
-        <v>7.6</v>
+        <v>7.3</v>
       </c>
     </row>
   </sheetData>
@@ -950,7 +917,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -988,10 +955,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1005,16 +972,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920262</v>
+        <v>22330051920265</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1028,22 +995,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920265</v>
+        <v>22330051920354</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1051,22 +1018,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920411</v>
+        <v>22330051920145</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1074,22 +1041,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920276</v>
+        <v>20330051920317</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="D6" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1097,139 +1064,24 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920354</v>
+        <v>22330051920017</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="D7" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920003</v>
-      </c>
-      <c r="B8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920017</v>
-      </c>
-      <c r="B9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>10</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920018</v>
-      </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>10</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920409</v>
-      </c>
-      <c r="B11" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>12</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920344</v>
-      </c>
-      <c r="B12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C12" t="s">
-        <v>20</v>
-      </c>
-      <c r="D12" t="s">
-        <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>11</v>
-      </c>
-      <c r="G12">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -100,6 +103,9 @@
     <t>QUERO</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
     <t>CASASOLA</t>
   </si>
   <si>
@@ -116,6 +122,9 @@
   </si>
   <si>
     <t>DIEGO JESUS</t>
+  </si>
+  <si>
+    <t>GUILLERMO SAUL</t>
   </si>
   <si>
     <t>SERGIO IVAN</t>
@@ -917,7 +926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -955,10 +964,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -972,16 +981,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920265</v>
+        <v>22330051920402</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -995,22 +1004,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920354</v>
+        <v>22330051920265</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1018,16 +1027,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920145</v>
+        <v>22330051920354</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D5" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1041,22 +1050,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920317</v>
+        <v>22330051920145</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1064,24 +1073,47 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920017</v>
+        <v>20330051920317</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920017</v>
+      </c>
+      <c r="B8" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D8" t="s">
+        <v>40</v>
+      </c>
+      <c r="E8" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" t="s">
         <v>10</v>
       </c>
-      <c r="G7">
+      <c r="G8">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="95" uniqueCount="44">
   <si>
     <t>Mat</t>
   </si>
@@ -88,6 +88,9 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
     <t>SOLANO</t>
   </si>
   <si>
@@ -109,6 +112,9 @@
     <t>CASASOLA</t>
   </si>
   <si>
+    <t>GALINDO</t>
+  </si>
+  <si>
     <t>MALDONADO</t>
   </si>
   <si>
@@ -128,6 +134,9 @@
   </si>
   <si>
     <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>BRANDON</t>
   </si>
   <si>
     <t>KEVIN</t>
@@ -926,7 +935,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -964,10 +973,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -987,10 +996,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1010,10 +1019,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1027,22 +1036,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920354</v>
+        <v>22330051920395</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1050,16 +1059,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920145</v>
+        <v>22330051920354</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1073,22 +1082,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920317</v>
+        <v>22330051920145</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1096,24 +1105,47 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>22330051920017</v>
+        <v>20330051920317</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920017</v>
+      </c>
+      <c r="B9" t="s">
+        <v>27</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" t="s">
+        <v>43</v>
+      </c>
+      <c r="E9" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" t="s">
         <v>10</v>
       </c>
-      <c r="G8">
+      <c r="G9">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
+++ b/docentes/Hernández Mendoza Delfina - Estadisticos 20222.xlsx
@@ -82,73 +82,73 @@
     <t>GARCIA</t>
   </si>
   <si>
+    <t>MEJIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
     <t>ROMERO</t>
   </si>
   <si>
     <t>SOLANO</t>
   </si>
   <si>
-    <t>TORRES</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
     <t>QUERO</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CASASOLA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>JERONIMO</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>CASASOLA</t>
-  </si>
-  <si>
     <t>GALINDO</t>
   </si>
   <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>SALAS</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
+    <t>JOSE FRANCISCO</t>
+  </si>
+  <si>
+    <t>SERGIO IVAN</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>LUIS</t>
+  </si>
+  <si>
     <t>GUILLERMO SAUL</t>
   </si>
   <si>
-    <t>SERGIO IVAN</t>
-  </si>
-  <si>
     <t>BRANDON</t>
   </si>
   <si>
     <t>KEVIN</t>
-  </si>
-  <si>
-    <t>MELISA VIANNEY</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>LUIS</t>
   </si>
 </sst>
 </file>
@@ -990,7 +990,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920402</v>
+        <v>22330051920021</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1005,7 +1005,7 @@
         <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1036,7 +1036,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920395</v>
+        <v>20330051920317</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1048,10 +1048,10 @@
         <v>39</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920354</v>
+        <v>22330051920017</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
@@ -1074,15 +1074,15 @@
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920145</v>
+        <v>22330051920402</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
@@ -1097,15 +1097,15 @@
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920317</v>
+        <v>22330051920395</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
@@ -1117,18 +1117,18 @@
         <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>22330051920017</v>
+        <v>22330051920354</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
@@ -1143,7 +1143,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>1</v>
